--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="187">
   <si>
     <t>#</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>暗金图鉴</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>粉色图鉴</t>
   </si>
   <si>
     <t>BOSS杀手</t>
@@ -818,12 +824,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1617,7 +1623,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M154"/>
+  <dimension ref="A1:M157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -2606,7 +2612,7 @@
         <v>7415</v>
       </c>
       <c r="H34" s="2">
-        <v>9000</v>
+        <v>10000</v>
       </c>
       <c r="I34" s="2">
         <v>3</v>
@@ -3790,7 +3796,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="82" customHeight="1" spans="3:12">
+    <row r="82" customHeight="1" spans="3:11">
       <c r="C82" s="1">
         <v>901</v>
       </c>
@@ -3819,7 +3825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" customHeight="1" spans="3:12">
+    <row r="83" customHeight="1" spans="3:11">
       <c r="C83" s="1">
         <v>902</v>
       </c>
@@ -3848,7 +3854,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" customHeight="1" spans="3:12">
+    <row r="84" customHeight="1" spans="3:11">
       <c r="C84" s="1">
         <v>903</v>
       </c>
@@ -3877,7 +3883,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" customHeight="1" spans="3:12">
+    <row r="85" customHeight="1" spans="3:11">
       <c r="C85" s="1">
         <v>904</v>
       </c>
@@ -3906,7 +3912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" customHeight="1" spans="3:12">
+    <row r="86" customHeight="1" spans="3:11">
       <c r="C86" s="1">
         <v>905</v>
       </c>
@@ -3935,7 +3941,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" customHeight="1" spans="3:12">
+    <row r="87" customHeight="1" spans="3:11">
       <c r="C87" s="1">
         <v>906</v>
       </c>
@@ -3964,7 +3970,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" customHeight="1" spans="3:12">
+    <row r="88" customHeight="1" spans="3:11">
       <c r="C88" s="1">
         <v>907</v>
       </c>
@@ -3993,7 +3999,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" customHeight="1" spans="3:12">
+    <row r="89" customHeight="1" spans="3:11">
       <c r="C89" s="1">
         <v>908</v>
       </c>
@@ -4022,7 +4028,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" customHeight="1" spans="3:12">
+    <row r="90" customHeight="1" spans="3:11">
       <c r="C90" s="1">
         <v>909</v>
       </c>
@@ -4051,7 +4057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="91" customHeight="1" spans="3:12">
+    <row r="91" customHeight="1" spans="3:11">
       <c r="C91" s="1">
         <v>910</v>
       </c>
@@ -4080,7 +4086,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" customHeight="1" spans="3:12">
+    <row r="92" customHeight="1" spans="3:11">
       <c r="C92" s="1">
         <v>911</v>
       </c>
@@ -4109,7 +4115,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="93" customHeight="1" spans="3:12">
+    <row r="93" customHeight="1" spans="3:11">
       <c r="C93" s="1">
         <v>912</v>
       </c>
@@ -4138,7 +4144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" customHeight="1" spans="3:12">
+    <row r="94" customHeight="1" spans="3:11">
       <c r="C94" s="1">
         <v>913</v>
       </c>
@@ -4167,50 +4173,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" customHeight="1" spans="3:12">
-      <c r="C96" s="1">
-        <v>10001</v>
-      </c>
-      <c r="D96" s="6">
-        <v>180001</v>
-      </c>
-      <c r="E96" s="1" t="s">
+    <row r="95" customHeight="1" spans="3:11">
+      <c r="C95" s="1">
+        <v>914</v>
+      </c>
+      <c r="D95" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="F96" s="1">
-        <v>2000</v>
-      </c>
-      <c r="G96" s="1">
-        <v>100</v>
-      </c>
-      <c r="H96" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I96" s="1">
-        <v>100</v>
-      </c>
-      <c r="J96" s="1">
-        <v>1</v>
-      </c>
-      <c r="K96" s="2">
-        <v>1</v>
-      </c>
-      <c r="L96" s="1" t="s">
+      <c r="E95" s="1" t="s">
         <v>104</v>
+      </c>
+      <c r="F95" s="1">
+        <v>2</v>
+      </c>
+      <c r="G95" s="1">
+        <v>8003</v>
+      </c>
+      <c r="H95" s="1">
+        <v>11000</v>
+      </c>
+      <c r="I95" s="1">
+        <v>4</v>
+      </c>
+      <c r="J95" s="1">
+        <v>10</v>
+      </c>
+      <c r="K95" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="97" customHeight="1" spans="3:12">
       <c r="C97" s="1">
-        <v>10002</v>
+        <v>10001</v>
       </c>
       <c r="D97" s="6">
-        <v>180002</v>
+        <v>180001</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>105</v>
       </c>
       <c r="F97" s="1">
-        <v>4000</v>
+        <v>2000</v>
       </c>
       <c r="G97" s="1">
         <v>100</v>
@@ -4228,21 +4231,21 @@
         <v>1</v>
       </c>
       <c r="L97" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="98" customHeight="1" spans="3:12">
       <c r="C98" s="1">
-        <v>10003</v>
+        <v>10002</v>
       </c>
       <c r="D98" s="6">
-        <v>180003</v>
+        <v>180002</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F98" s="1">
-        <v>150000</v>
+        <v>4000</v>
       </c>
       <c r="G98" s="1">
         <v>100</v>
@@ -4254,27 +4257,27 @@
         <v>100</v>
       </c>
       <c r="J98" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K98" s="2">
         <v>1</v>
       </c>
       <c r="L98" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="99" customHeight="1" spans="3:12">
       <c r="C99" s="1">
-        <v>10004</v>
+        <v>10003</v>
       </c>
       <c r="D99" s="6">
-        <v>180004</v>
+        <v>180003</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F99" s="1">
-        <v>8000</v>
+        <v>150000</v>
       </c>
       <c r="G99" s="1">
         <v>100</v>
@@ -4286,27 +4289,27 @@
         <v>100</v>
       </c>
       <c r="J99" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K99" s="2">
         <v>1</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="100" customHeight="1" spans="3:12">
       <c r="C100" s="1">
-        <v>10005</v>
+        <v>10004</v>
       </c>
       <c r="D100" s="6">
-        <v>180005</v>
+        <v>180004</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F100" s="1">
-        <v>3000</v>
+        <v>8000</v>
       </c>
       <c r="G100" s="1">
         <v>100</v>
@@ -4324,21 +4327,21 @@
         <v>1</v>
       </c>
       <c r="L100" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="101" customHeight="1" spans="3:12">
       <c r="C101" s="1">
-        <v>10006</v>
+        <v>10005</v>
       </c>
       <c r="D101" s="6">
-        <v>180006</v>
+        <v>180005</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F101" s="1">
-        <v>50000</v>
+        <v>3000</v>
       </c>
       <c r="G101" s="1">
         <v>100</v>
@@ -4350,27 +4353,27 @@
         <v>100</v>
       </c>
       <c r="J101" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K101" s="2">
         <v>1</v>
       </c>
       <c r="L101" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="102" customHeight="1" spans="3:12">
       <c r="C102" s="1">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="D102" s="6">
-        <v>180007</v>
+        <v>180006</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F102" s="1">
-        <v>2000</v>
+        <v>50000</v>
       </c>
       <c r="G102" s="1">
         <v>100</v>
@@ -4382,27 +4385,27 @@
         <v>100</v>
       </c>
       <c r="J102" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K102" s="2">
         <v>1</v>
       </c>
       <c r="L102" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="103" customHeight="1" spans="3:12">
       <c r="C103" s="1">
-        <v>10008</v>
+        <v>10007</v>
       </c>
       <c r="D103" s="6">
-        <v>180008</v>
+        <v>180007</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F103" s="1">
-        <v>20000</v>
+        <v>2000</v>
       </c>
       <c r="G103" s="1">
         <v>100</v>
@@ -4414,27 +4417,27 @@
         <v>100</v>
       </c>
       <c r="J103" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K103" s="2">
         <v>1</v>
       </c>
       <c r="L103" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="104" customHeight="1" spans="3:12">
       <c r="C104" s="1">
-        <v>10009</v>
+        <v>10008</v>
       </c>
       <c r="D104" s="6">
-        <v>180009</v>
+        <v>180008</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F104" s="1">
-        <v>3000</v>
+        <v>20000</v>
       </c>
       <c r="G104" s="1">
         <v>100</v>
@@ -4446,27 +4449,27 @@
         <v>100</v>
       </c>
       <c r="J104" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K104" s="2">
         <v>1</v>
       </c>
       <c r="L104" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="105" customHeight="1" spans="3:12">
       <c r="C105" s="1">
-        <v>10010</v>
+        <v>10009</v>
       </c>
       <c r="D105" s="6">
-        <v>180010</v>
+        <v>180009</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F105" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="G105" s="1">
         <v>100</v>
@@ -4484,21 +4487,21 @@
         <v>1</v>
       </c>
       <c r="L105" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="106" customHeight="1" spans="3:12">
       <c r="C106" s="1">
-        <v>10011</v>
+        <v>10010</v>
       </c>
       <c r="D106" s="6">
-        <v>180011</v>
+        <v>180010</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="F106" s="1">
-        <v>100000</v>
+        <v>10000</v>
       </c>
       <c r="G106" s="1">
         <v>100</v>
@@ -4510,24 +4513,24 @@
         <v>100</v>
       </c>
       <c r="J106" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K106" s="2">
         <v>1</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="107" customHeight="1" spans="3:12">
       <c r="C107" s="1">
-        <v>10012</v>
+        <v>10011</v>
       </c>
       <c r="D107" s="6">
-        <v>180012</v>
+        <v>180011</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F107" s="1">
         <v>100000</v>
@@ -4548,21 +4551,21 @@
         <v>1</v>
       </c>
       <c r="L107" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="108" customHeight="1" spans="3:12">
       <c r="C108" s="1">
-        <v>10013</v>
+        <v>10012</v>
       </c>
       <c r="D108" s="6">
-        <v>180013</v>
+        <v>180012</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F108" s="1">
-        <v>50000</v>
+        <v>100000</v>
       </c>
       <c r="G108" s="1">
         <v>100</v>
@@ -4580,21 +4583,21 @@
         <v>1</v>
       </c>
       <c r="L108" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="109" customHeight="1" spans="3:12">
       <c r="C109" s="1">
-        <v>10014</v>
+        <v>10013</v>
       </c>
       <c r="D109" s="6">
-        <v>180014</v>
+        <v>180013</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F109" s="1">
-        <v>100000</v>
+        <v>50000</v>
       </c>
       <c r="G109" s="1">
         <v>100</v>
@@ -4612,18 +4615,18 @@
         <v>1</v>
       </c>
       <c r="L109" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="110" customHeight="1" spans="3:12">
       <c r="C110" s="1">
-        <v>10015</v>
+        <v>10014</v>
       </c>
       <c r="D110" s="6">
-        <v>180015</v>
+        <v>180014</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F110" s="1">
         <v>100000</v>
@@ -4644,21 +4647,21 @@
         <v>1</v>
       </c>
       <c r="L110" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="111" customHeight="1" spans="3:12">
       <c r="C111" s="1">
-        <v>10016</v>
+        <v>10015</v>
       </c>
       <c r="D111" s="6">
-        <v>180020</v>
+        <v>180015</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F111" s="1">
-        <v>30000</v>
+        <v>100000</v>
       </c>
       <c r="G111" s="1">
         <v>100</v>
@@ -4670,24 +4673,24 @@
         <v>100</v>
       </c>
       <c r="J111" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K111" s="2">
         <v>1</v>
       </c>
       <c r="L111" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="112" customHeight="1" spans="3:12">
       <c r="C112" s="1">
-        <v>10017</v>
+        <v>10016</v>
       </c>
       <c r="D112" s="6">
-        <v>180021</v>
+        <v>180020</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F112" s="1">
         <v>30000</v>
@@ -4708,21 +4711,21 @@
         <v>1</v>
       </c>
       <c r="L112" s="1" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="113" customHeight="1" spans="1:12">
       <c r="C113" s="1">
-        <v>10018</v>
+        <v>10017</v>
       </c>
       <c r="D113" s="6">
-        <v>180022</v>
+        <v>180021</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F113" s="1">
-        <v>3000</v>
+        <v>30000</v>
       </c>
       <c r="G113" s="1">
         <v>100</v>
@@ -4734,65 +4737,65 @@
         <v>100</v>
       </c>
       <c r="J113" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K113" s="2">
         <v>1</v>
       </c>
       <c r="L113" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="115" customHeight="1" spans="1:12">
-      <c r="C115" s="1">
-        <v>10030</v>
-      </c>
-      <c r="D115" s="1">
-        <v>180030</v>
-      </c>
-      <c r="E115" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="F115" s="1">
-        <v>5</v>
-      </c>
-      <c r="G115" s="1">
-        <v>1100</v>
-      </c>
-      <c r="H115" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I115" s="1">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="114" customHeight="1" spans="1:12">
+      <c r="C114" s="1">
+        <v>10018</v>
+      </c>
+      <c r="D114" s="6">
+        <v>180022</v>
+      </c>
+      <c r="E114" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="F114" s="1">
+        <v>3000</v>
+      </c>
+      <c r="G114" s="1">
         <v>100</v>
       </c>
-      <c r="J115" s="1">
-        <v>1</v>
-      </c>
-      <c r="K115" s="2">
-        <v>1</v>
-      </c>
-      <c r="L115" s="1" t="s">
-        <v>123</v>
+      <c r="H114" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I114" s="1">
+        <v>100</v>
+      </c>
+      <c r="J114" s="1">
+        <v>1</v>
+      </c>
+      <c r="K114" s="2">
+        <v>1</v>
+      </c>
+      <c r="L114" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="116" customHeight="1" spans="1:12">
       <c r="C116" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D116" s="6">
-        <v>180032</v>
+        <v>10030</v>
+      </c>
+      <c r="D116" s="1">
+        <v>180030</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>124</v>
       </c>
       <c r="F116" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G116" s="1">
         <v>1100</v>
       </c>
       <c r="H116" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I116" s="1">
         <v>100</v>
@@ -4804,24 +4807,24 @@
         <v>1</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="117" customHeight="1" spans="1:12">
       <c r="C117" s="1">
-        <v>10032</v>
+        <v>10031</v>
       </c>
       <c r="D117" s="6">
-        <v>180033</v>
+        <v>180032</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F117" s="1">
         <v>1</v>
       </c>
       <c r="G117" s="1">
-        <v>1600</v>
+        <v>1100</v>
       </c>
       <c r="H117" s="1">
         <v>2000</v>
@@ -4836,27 +4839,27 @@
         <v>1</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="118" customHeight="1" spans="1:12">
       <c r="C118" s="1">
-        <v>10033</v>
+        <v>10032</v>
       </c>
       <c r="D118" s="6">
-        <v>180034</v>
+        <v>180033</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F118" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G118" s="1">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="H118" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="I118" s="1">
         <v>100</v>
@@ -4868,27 +4871,27 @@
         <v>1</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="119" customHeight="1" spans="1:12">
       <c r="C119" s="1">
-        <v>10034</v>
+        <v>10033</v>
       </c>
       <c r="D119" s="6">
-        <v>180035</v>
+        <v>180034</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F119" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G119" s="1">
-        <v>2000</v>
+        <v>1100</v>
       </c>
       <c r="H119" s="1">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="I119" s="1">
         <v>100</v>
@@ -4900,18 +4903,18 @@
         <v>1</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="120" customHeight="1" spans="1:12">
       <c r="C120" s="1">
-        <v>10035</v>
+        <v>10034</v>
       </c>
       <c r="D120" s="6">
-        <v>180036</v>
+        <v>180035</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F120" s="1">
         <v>1</v>
@@ -4932,27 +4935,27 @@
         <v>1</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="121" customHeight="1" spans="1:12">
       <c r="C121" s="1">
-        <v>10036</v>
+        <v>10035</v>
       </c>
       <c r="D121" s="6">
-        <v>180037</v>
+        <v>180036</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F121" s="1">
         <v>1</v>
       </c>
       <c r="G121" s="1">
+        <v>2000</v>
+      </c>
+      <c r="H121" s="1">
         <v>2500</v>
-      </c>
-      <c r="H121" s="1">
-        <v>3500</v>
       </c>
       <c r="I121" s="1">
         <v>100</v>
@@ -4964,24 +4967,24 @@
         <v>1</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="122" customHeight="1" spans="1:12">
       <c r="C122" s="1">
-        <v>10037</v>
+        <v>10036</v>
       </c>
       <c r="D122" s="6">
-        <v>180038</v>
+        <v>180037</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F122" s="1">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G122" s="1">
-        <v>1600</v>
+        <v>2500</v>
       </c>
       <c r="H122" s="1">
         <v>3500</v>
@@ -4996,24 +4999,24 @@
         <v>1</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="123" customHeight="1" spans="1:12">
       <c r="C123" s="1">
-        <v>10038</v>
+        <v>10037</v>
       </c>
       <c r="D123" s="6">
-        <v>180039</v>
+        <v>180038</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F123" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G123" s="1">
-        <v>2000</v>
+        <v>1600</v>
       </c>
       <c r="H123" s="1">
         <v>3500</v>
@@ -5028,33 +5031,27 @@
         <v>1</v>
       </c>
       <c r="L123" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="124" customHeight="1" spans="1:12">
-      <c r="A124" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B124" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="C124" s="1">
-        <v>10039</v>
+        <v>10038</v>
       </c>
       <c r="D124" s="6">
-        <v>180040</v>
+        <v>180039</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="F124" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G124" s="1">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="H124" s="1">
-        <v>4000</v>
+        <v>3500</v>
       </c>
       <c r="I124" s="1">
         <v>100</v>
@@ -5066,27 +5063,33 @@
         <v>1</v>
       </c>
       <c r="L124" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="125" customHeight="1" spans="1:12">
+      <c r="A125" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C125" s="1">
-        <v>10040</v>
+        <v>10039</v>
       </c>
       <c r="D125" s="6">
-        <v>180041</v>
+        <v>180040</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F125" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G125" s="1">
+        <v>3000</v>
+      </c>
+      <c r="H125" s="1">
         <v>4000</v>
-      </c>
-      <c r="H125" s="1">
-        <v>5000</v>
       </c>
       <c r="I125" s="1">
         <v>100</v>
@@ -5098,27 +5101,27 @@
         <v>1</v>
       </c>
       <c r="L125" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="126" customHeight="1" spans="1:12">
       <c r="C126" s="1">
-        <v>10041</v>
+        <v>10040</v>
       </c>
       <c r="D126" s="6">
-        <v>180042</v>
+        <v>180041</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F126" s="1">
         <v>3</v>
       </c>
       <c r="G126" s="1">
+        <v>4000</v>
+      </c>
+      <c r="H126" s="1">
         <v>5000</v>
-      </c>
-      <c r="H126" s="1">
-        <v>6000</v>
       </c>
       <c r="I126" s="1">
         <v>100</v>
@@ -5130,27 +5133,27 @@
         <v>1</v>
       </c>
       <c r="L126" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="127" customHeight="1" spans="1:12">
       <c r="C127" s="1">
-        <v>10042</v>
+        <v>10041</v>
       </c>
       <c r="D127" s="6">
-        <v>180043</v>
+        <v>180042</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F127" s="1">
         <v>3</v>
       </c>
       <c r="G127" s="1">
+        <v>5000</v>
+      </c>
+      <c r="H127" s="1">
         <v>6000</v>
-      </c>
-      <c r="H127" s="1">
-        <v>7000</v>
       </c>
       <c r="I127" s="1">
         <v>100</v>
@@ -5162,27 +5165,27 @@
         <v>1</v>
       </c>
       <c r="L127" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="128" customHeight="1" spans="1:12">
       <c r="C128" s="1">
-        <v>10043</v>
+        <v>10042</v>
       </c>
       <c r="D128" s="6">
-        <v>180044</v>
+        <v>180043</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="F128" s="1">
         <v>3</v>
       </c>
       <c r="G128" s="1">
+        <v>6000</v>
+      </c>
+      <c r="H128" s="1">
         <v>7000</v>
-      </c>
-      <c r="H128" s="1">
-        <v>8000</v>
       </c>
       <c r="I128" s="1">
         <v>100</v>
@@ -5194,27 +5197,27 @@
         <v>1</v>
       </c>
       <c r="L128" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="129" customHeight="1" spans="3:12">
       <c r="C129" s="1">
-        <v>10044</v>
+        <v>10043</v>
       </c>
       <c r="D129" s="6">
-        <v>180045</v>
+        <v>180044</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F129" s="1">
         <v>3</v>
       </c>
       <c r="G129" s="1">
+        <v>7000</v>
+      </c>
+      <c r="H129" s="1">
         <v>8000</v>
-      </c>
-      <c r="H129" s="1">
-        <v>9000</v>
       </c>
       <c r="I129" s="1">
         <v>100</v>
@@ -5226,44 +5229,44 @@
         <v>1</v>
       </c>
       <c r="L129" s="1" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="131" customHeight="1" spans="3:12">
-      <c r="C131" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D131" s="9" t="s">
-        <v>138</v>
-      </c>
-      <c r="E131" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="130" customHeight="1" spans="3:12">
+      <c r="C130" s="1">
+        <v>10044</v>
+      </c>
+      <c r="D130" s="6">
+        <v>180045</v>
+      </c>
+      <c r="E130" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="F131" s="1">
-        <v>5</v>
-      </c>
-      <c r="G131" s="1">
-        <v>150</v>
-      </c>
-      <c r="H131" s="1">
-        <v>1200</v>
-      </c>
-      <c r="I131" s="1">
-        <v>20</v>
-      </c>
-      <c r="J131" s="1">
-        <v>2</v>
-      </c>
-      <c r="K131" s="2">
-        <v>1</v>
-      </c>
-      <c r="L131" s="1" t="s">
-        <v>39</v>
+      <c r="F130" s="1">
+        <v>3</v>
+      </c>
+      <c r="G130" s="1">
+        <v>8000</v>
+      </c>
+      <c r="H130" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I130" s="1">
+        <v>100</v>
+      </c>
+      <c r="J130" s="1">
+        <v>1</v>
+      </c>
+      <c r="K130" s="2">
+        <v>1</v>
+      </c>
+      <c r="L130" s="1" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="132" customHeight="1" spans="3:12">
       <c r="C132" s="1">
-        <v>11002</v>
+        <v>11001</v>
       </c>
       <c r="D132" s="9" t="s">
         <v>140</v>
@@ -5275,13 +5278,13 @@
         <v>5</v>
       </c>
       <c r="G132" s="1">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="H132" s="1">
-        <v>1000</v>
+        <v>1200</v>
       </c>
       <c r="I132" s="1">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J132" s="1">
         <v>2</v>
@@ -5295,7 +5298,7 @@
     </row>
     <row r="133" customHeight="1" spans="3:12">
       <c r="C133" s="1">
-        <v>11003</v>
+        <v>11002</v>
       </c>
       <c r="D133" s="9" t="s">
         <v>142</v>
@@ -5304,16 +5307,16 @@
         <v>143</v>
       </c>
       <c r="F133" s="1">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G133" s="1">
-        <v>1050</v>
+        <v>200</v>
       </c>
       <c r="H133" s="1">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="I133" s="1">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="J133" s="1">
         <v>2</v>
@@ -5327,25 +5330,25 @@
     </row>
     <row r="134" customHeight="1" spans="3:12">
       <c r="C134" s="1">
-        <v>11004</v>
+        <v>11003</v>
       </c>
       <c r="D134" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F134" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="G134" s="1">
-        <v>4001</v>
+        <v>1050</v>
       </c>
       <c r="H134" s="1">
-        <v>6000</v>
+        <v>1500</v>
       </c>
       <c r="I134" s="1">
-        <v>79</v>
+        <v>51</v>
       </c>
       <c r="J134" s="1">
         <v>2</v>
@@ -5359,54 +5362,54 @@
     </row>
     <row r="135" customHeight="1" spans="3:12">
       <c r="C135" s="1">
-        <v>11005</v>
+        <v>11004</v>
       </c>
       <c r="D135" s="9" t="s">
         <v>144</v>
       </c>
-      <c r="E135" s="7" t="s">
+      <c r="E135" s="1" t="s">
         <v>145</v>
       </c>
       <c r="F135" s="1">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="G135" s="1">
-        <v>101</v>
+        <v>4001</v>
       </c>
       <c r="H135" s="1">
-        <v>500</v>
+        <v>6000</v>
       </c>
       <c r="I135" s="1">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="J135" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K135" s="2">
         <v>1</v>
       </c>
       <c r="L135" s="1" t="s">
-        <v>146</v>
+        <v>39</v>
       </c>
     </row>
     <row r="136" customHeight="1" spans="3:12">
       <c r="C136" s="1">
-        <v>11006</v>
+        <v>11005</v>
       </c>
       <c r="D136" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="E136" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="E136" s="7" t="s">
-        <v>148</v>
-      </c>
       <c r="F136" s="1">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="G136" s="1">
-        <v>501</v>
+        <v>101</v>
       </c>
       <c r="H136" s="1">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="I136" s="1">
         <v>10</v>
@@ -5418,59 +5421,59 @@
         <v>1</v>
       </c>
       <c r="L136" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="137" customHeight="1" spans="3:12">
       <c r="C137" s="1">
-        <v>11007</v>
+        <v>11006</v>
       </c>
       <c r="D137" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="E137" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="E137" s="7" t="s">
+      <c r="F137" s="1">
+        <v>15</v>
+      </c>
+      <c r="G137" s="1">
+        <v>501</v>
+      </c>
+      <c r="H137" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I137" s="1">
+        <v>10</v>
+      </c>
+      <c r="J137" s="1">
+        <v>1</v>
+      </c>
+      <c r="K137" s="2">
+        <v>1</v>
+      </c>
+      <c r="L137" s="1" t="s">
         <v>151</v>
-      </c>
-      <c r="F137" s="1">
-        <v>10</v>
-      </c>
-      <c r="G137" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H137" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I137" s="1">
-        <v>20</v>
-      </c>
-      <c r="J137" s="1">
-        <v>1</v>
-      </c>
-      <c r="K137" s="2">
-        <v>1</v>
-      </c>
-      <c r="L137" s="1" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="138" customHeight="1" spans="3:12">
       <c r="C138" s="1">
-        <v>11008</v>
+        <v>11007</v>
       </c>
       <c r="D138" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="E138" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="E138" s="7" t="s">
-        <v>154</v>
-      </c>
       <c r="F138" s="1">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G138" s="1">
-        <v>1501</v>
+        <v>1001</v>
       </c>
       <c r="H138" s="1">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I138" s="1">
         <v>20</v>
@@ -5482,59 +5485,59 @@
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="139" customHeight="1" spans="3:12">
       <c r="C139" s="1">
-        <v>11009</v>
+        <v>11008</v>
       </c>
       <c r="D139" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E139" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E139" s="7" t="s">
+      <c r="F139" s="1">
+        <v>8</v>
+      </c>
+      <c r="G139" s="1">
+        <v>1501</v>
+      </c>
+      <c r="H139" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I139" s="1">
+        <v>20</v>
+      </c>
+      <c r="J139" s="1">
+        <v>1</v>
+      </c>
+      <c r="K139" s="2">
+        <v>1</v>
+      </c>
+      <c r="L139" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="F139" s="1">
-        <v>15</v>
-      </c>
-      <c r="G139" s="1">
-        <v>2001</v>
-      </c>
-      <c r="H139" s="1">
-        <v>2500</v>
-      </c>
-      <c r="I139" s="1">
-        <v>52</v>
-      </c>
-      <c r="J139" s="1">
-        <v>1</v>
-      </c>
-      <c r="K139" s="2">
-        <v>1</v>
-      </c>
-      <c r="L139" s="1" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="140" customHeight="1" spans="3:12">
       <c r="C140" s="1">
-        <v>11010</v>
+        <v>11009</v>
       </c>
       <c r="D140" s="9" t="s">
+        <v>158</v>
+      </c>
+      <c r="E140" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="E140" s="7" t="s">
-        <v>160</v>
-      </c>
       <c r="F140" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G140" s="1">
-        <v>2501</v>
+        <v>2001</v>
       </c>
       <c r="H140" s="1">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="I140" s="1">
         <v>52</v>
@@ -5546,123 +5549,126 @@
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="141" customHeight="1" spans="3:12">
       <c r="C141" s="1">
-        <v>11011</v>
+        <v>11010</v>
       </c>
       <c r="D141" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="E141" s="7" t="s">
         <v>162</v>
       </c>
-      <c r="E141" s="7" t="s">
+      <c r="F141" s="1">
+        <v>7</v>
+      </c>
+      <c r="G141" s="1">
+        <v>2501</v>
+      </c>
+      <c r="H141" s="1">
+        <v>3000</v>
+      </c>
+      <c r="I141" s="1">
+        <v>52</v>
+      </c>
+      <c r="J141" s="1">
+        <v>1</v>
+      </c>
+      <c r="K141" s="2">
+        <v>1</v>
+      </c>
+      <c r="L141" s="1" t="s">
         <v>163</v>
-      </c>
-      <c r="F141" s="1">
-        <v>3</v>
-      </c>
-      <c r="G141" s="1">
-        <v>3001</v>
-      </c>
-      <c r="H141" s="1">
-        <v>3800</v>
-      </c>
-      <c r="I141" s="1">
-        <v>62</v>
-      </c>
-      <c r="J141" s="1">
-        <v>1</v>
-      </c>
-      <c r="K141" s="2">
-        <v>1</v>
-      </c>
-      <c r="L141" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="142" customHeight="1" spans="3:12">
       <c r="C142" s="1">
-        <v>11012</v>
+        <v>11011</v>
       </c>
       <c r="D142" s="9" t="s">
+        <v>164</v>
+      </c>
+      <c r="E142" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="E142" s="7" t="s">
+      <c r="F142" s="1">
+        <v>3</v>
+      </c>
+      <c r="G142" s="1">
+        <v>3001</v>
+      </c>
+      <c r="H142" s="1">
+        <v>3800</v>
+      </c>
+      <c r="I142" s="1">
+        <v>62</v>
+      </c>
+      <c r="J142" s="1">
+        <v>1</v>
+      </c>
+      <c r="K142" s="2">
+        <v>1</v>
+      </c>
+      <c r="L142" s="1" t="s">
         <v>166</v>
-      </c>
-      <c r="F142" s="2">
-        <v>1</v>
-      </c>
-      <c r="G142" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H142" s="2">
-        <v>6000</v>
-      </c>
-      <c r="I142" s="2">
-        <v>61</v>
-      </c>
-      <c r="J142" s="2">
-        <v>1</v>
-      </c>
-      <c r="K142" s="2">
-        <v>1</v>
-      </c>
-      <c r="L142" s="1" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="143" customHeight="1" spans="3:12">
       <c r="C143" s="1">
-        <v>11013</v>
+        <v>11012</v>
       </c>
       <c r="D143" s="9" t="s">
         <v>167</v>
       </c>
-      <c r="E143" s="1" t="s">
+      <c r="E143" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="F143" s="1">
-        <v>3</v>
-      </c>
-      <c r="G143" s="1">
-        <v>5501</v>
-      </c>
-      <c r="H143" s="1">
-        <v>6500</v>
-      </c>
-      <c r="I143" s="1">
-        <v>47</v>
-      </c>
-      <c r="J143" s="1">
+      <c r="F143" s="2">
+        <v>1</v>
+      </c>
+      <c r="G143" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H143" s="2">
+        <v>6000</v>
+      </c>
+      <c r="I143" s="2">
+        <v>61</v>
+      </c>
+      <c r="J143" s="2">
         <v>1</v>
       </c>
       <c r="K143" s="2">
         <v>1</v>
+      </c>
+      <c r="L143" s="1" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="144" customHeight="1" spans="3:12">
       <c r="C144" s="1">
-        <v>11014</v>
+        <v>11013</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>162</v>
-      </c>
-      <c r="E144" s="7" t="s">
-        <v>163</v>
+        <v>169</v>
+      </c>
+      <c r="E144" s="1" t="s">
+        <v>170</v>
       </c>
       <c r="F144" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G144" s="1">
         <v>5501</v>
       </c>
       <c r="H144" s="1">
-        <v>6500</v>
+        <v>7500</v>
       </c>
       <c r="I144" s="1">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="J144" s="1">
         <v>1</v>
@@ -5673,25 +5679,25 @@
     </row>
     <row r="145" customHeight="1" spans="3:12">
       <c r="C145" s="1">
-        <v>11015</v>
+        <v>11014</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="F145" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>6401</v>
+        <v>5501</v>
       </c>
       <c r="H145" s="1">
-        <v>7400</v>
+        <v>6500</v>
       </c>
       <c r="I145" s="1">
-        <v>91</v>
+        <v>67</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
@@ -5702,150 +5708,83 @@
     </row>
     <row r="146" customHeight="1" spans="3:12">
       <c r="C146" s="1">
-        <v>11016</v>
+        <v>11015</v>
       </c>
       <c r="D146" s="9" t="s">
         <v>171</v>
       </c>
-      <c r="E146" s="1" t="s">
+      <c r="E146" s="7" t="s">
         <v>172</v>
       </c>
       <c r="F146" s="1">
+        <v>1</v>
+      </c>
+      <c r="G146" s="1">
+        <v>6401</v>
+      </c>
+      <c r="H146" s="1">
+        <v>8400</v>
+      </c>
+      <c r="I146" s="1">
+        <v>91</v>
+      </c>
+      <c r="J146" s="1">
+        <v>1</v>
+      </c>
+      <c r="K146" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" customHeight="1" spans="3:12">
+      <c r="C147" s="1">
+        <v>11016</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E147" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="F147" s="1">
         <v>2</v>
       </c>
-      <c r="G146" s="1">
+      <c r="G147" s="1">
         <v>8001</v>
       </c>
-      <c r="H146" s="1">
-        <v>9000</v>
-      </c>
-      <c r="I146" s="1">
+      <c r="H147" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I147" s="1">
         <v>53</v>
       </c>
-      <c r="J146" s="1">
-        <v>1</v>
-      </c>
-      <c r="K146" s="2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="148" customHeight="1" spans="3:12">
-      <c r="C148" s="1">
-        <v>11303</v>
-      </c>
-      <c r="D148" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E148" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="F148" s="1">
-        <v>10</v>
-      </c>
-      <c r="G148" s="1">
-        <v>3903</v>
-      </c>
-      <c r="H148" s="1">
-        <v>4402</v>
-      </c>
-      <c r="I148" s="1">
-        <v>37</v>
-      </c>
-      <c r="J148" s="1">
-        <v>1</v>
-      </c>
-      <c r="K148" s="2">
-        <v>1</v>
-      </c>
-      <c r="L148" s="1" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="149" customHeight="1" spans="3:12">
-      <c r="C149" s="1">
-        <v>11304</v>
-      </c>
-      <c r="D149" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E149" s="7" t="s">
-        <v>176</v>
-      </c>
-      <c r="F149" s="1">
-        <v>8</v>
-      </c>
-      <c r="G149" s="1">
-        <v>4403</v>
-      </c>
-      <c r="H149" s="1">
-        <v>4902</v>
-      </c>
-      <c r="I149" s="1">
-        <v>41</v>
-      </c>
-      <c r="J149" s="1">
-        <v>1</v>
-      </c>
-      <c r="K149" s="2">
-        <v>1</v>
-      </c>
-      <c r="L149" s="1" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="150" customHeight="1" spans="3:12">
-      <c r="C150" s="1">
-        <v>11305</v>
-      </c>
-      <c r="D150" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E150" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="F150" s="1">
-        <v>6</v>
-      </c>
-      <c r="G150" s="1">
-        <v>4903</v>
-      </c>
-      <c r="H150" s="1">
-        <v>5402</v>
-      </c>
-      <c r="I150" s="1">
-        <v>47</v>
-      </c>
-      <c r="J150" s="1">
-        <v>1</v>
-      </c>
-      <c r="K150" s="2">
-        <v>1</v>
-      </c>
-      <c r="L150" s="1" t="s">
-        <v>152</v>
+      <c r="J147" s="1">
+        <v>1</v>
+      </c>
+      <c r="K147" s="2">
+        <v>1</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1">
-        <v>11306</v>
+        <v>11303</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="F151" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G151" s="1">
-        <v>5403</v>
+        <v>3903</v>
       </c>
       <c r="H151" s="1">
-        <v>6402</v>
+        <v>4402</v>
       </c>
       <c r="I151" s="1">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="J151" s="1">
         <v>1</v>
@@ -5854,30 +5793,30 @@
         <v>1</v>
       </c>
       <c r="L151" s="1" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1">
-        <v>11307</v>
+        <v>11304</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="F152" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G152" s="1">
-        <v>6403</v>
+        <v>4403</v>
       </c>
       <c r="H152" s="1">
-        <v>7402</v>
+        <v>4902</v>
       </c>
       <c r="I152" s="1">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="J152" s="1">
         <v>1</v>
@@ -5886,45 +5825,141 @@
         <v>1</v>
       </c>
       <c r="L152" s="1" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1">
+        <v>11305</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>179</v>
+      </c>
+      <c r="E153" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="F153" s="1">
+        <v>6</v>
+      </c>
+      <c r="G153" s="1">
+        <v>4903</v>
+      </c>
+      <c r="H153" s="1">
+        <v>5402</v>
+      </c>
+      <c r="I153" s="1">
+        <v>47</v>
+      </c>
+      <c r="J153" s="1">
+        <v>1</v>
+      </c>
+      <c r="K153" s="2">
+        <v>1</v>
+      </c>
+      <c r="L153" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="154" customHeight="1" spans="3:12">
+      <c r="C154" s="1">
+        <v>11306</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>181</v>
+      </c>
+      <c r="E154" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="F154" s="1">
+        <v>4</v>
+      </c>
+      <c r="G154" s="1">
+        <v>5403</v>
+      </c>
+      <c r="H154" s="1">
+        <v>6402</v>
+      </c>
+      <c r="I154" s="1">
+        <v>51</v>
+      </c>
+      <c r="J154" s="1">
+        <v>1</v>
+      </c>
+      <c r="K154" s="2">
+        <v>1</v>
+      </c>
+      <c r="L154" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="155" customHeight="1" spans="3:12">
+      <c r="C155" s="1">
+        <v>11307</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>183</v>
+      </c>
+      <c r="E155" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="F155" s="1">
+        <v>3</v>
+      </c>
+      <c r="G155" s="1">
+        <v>6403</v>
+      </c>
+      <c r="H155" s="1">
+        <v>7402</v>
+      </c>
+      <c r="I155" s="1">
+        <v>61</v>
+      </c>
+      <c r="J155" s="1">
+        <v>1</v>
+      </c>
+      <c r="K155" s="2">
+        <v>1</v>
+      </c>
+      <c r="L155" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="156" customHeight="1" spans="3:12">
+      <c r="C156" s="1">
         <v>11308</v>
       </c>
-      <c r="D153" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="F153" s="1">
-        <v>1</v>
-      </c>
-      <c r="G153" s="1">
+      <c r="D156" s="9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E156" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="F156" s="1">
+        <v>1</v>
+      </c>
+      <c r="G156" s="1">
         <v>7403</v>
       </c>
-      <c r="H153" s="1">
-        <v>8402</v>
-      </c>
-      <c r="I153" s="1">
+      <c r="H156" s="1">
+        <v>9402</v>
+      </c>
+      <c r="I156" s="1">
         <v>79</v>
       </c>
-      <c r="J153" s="1">
-        <v>1</v>
-      </c>
-      <c r="K153" s="2">
-        <v>1</v>
-      </c>
-      <c r="L153" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="154" customHeight="1" spans="3:12">
-      <c r="D154" s="5"/>
-      <c r="E154" s="7"/>
-      <c r="K154" s="2"/>
+      <c r="J156" s="1">
+        <v>1</v>
+      </c>
+      <c r="K156" s="2">
+        <v>1</v>
+      </c>
+      <c r="L156" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="157" customHeight="1" spans="3:12">
+      <c r="D157" s="5"/>
+      <c r="E157" s="7"/>
+      <c r="K157" s="2"/>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="193">
   <si>
     <t>#</t>
   </si>
@@ -593,6 +593,18 @@
     <t>六大道戒</t>
   </si>
   <si>
+    <t>220045</t>
+  </si>
+  <si>
+    <t>粉色魂心</t>
+  </si>
+  <si>
+    <t>220046</t>
+  </si>
+  <si>
+    <t>暗金兽魂</t>
+  </si>
+  <si>
     <t>220303</t>
   </si>
   <si>
@@ -627,6 +639,12 @@
   </si>
   <si>
     <t>暗金坐骑</t>
+  </si>
+  <si>
+    <t>220309</t>
+  </si>
+  <si>
+    <t>粉色坐骑</t>
   </si>
 </sst>
 </file>
@@ -824,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -5627,7 +5645,7 @@
         <v>168</v>
       </c>
       <c r="F143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G143" s="2">
         <v>5001</v>
@@ -5764,15 +5782,73 @@
         <v>1</v>
       </c>
     </row>
+    <row r="148" customHeight="1" spans="3:12">
+      <c r="C148" s="1">
+        <v>11017</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="E148" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F148" s="1">
+        <v>2</v>
+      </c>
+      <c r="G148" s="1">
+        <v>8501</v>
+      </c>
+      <c r="H148" s="1">
+        <v>9500</v>
+      </c>
+      <c r="I148" s="1">
+        <v>59</v>
+      </c>
+      <c r="J148" s="1">
+        <v>1</v>
+      </c>
+      <c r="K148" s="2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="149" customHeight="1" spans="3:12">
+      <c r="C149" s="1">
+        <v>11018</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>177</v>
+      </c>
+      <c r="E149" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F149" s="1">
+        <v>2</v>
+      </c>
+      <c r="G149" s="1">
+        <v>9001</v>
+      </c>
+      <c r="H149" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I149" s="1">
+        <v>61</v>
+      </c>
+      <c r="J149" s="1">
+        <v>1</v>
+      </c>
+      <c r="K149" s="2">
+        <v>1</v>
+      </c>
+    </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1">
         <v>11303</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F151" s="1">
         <v>10</v>
@@ -5781,7 +5857,7 @@
         <v>3903</v>
       </c>
       <c r="H151" s="1">
-        <v>4402</v>
+        <v>4500</v>
       </c>
       <c r="I151" s="1">
         <v>37</v>
@@ -5801,10 +5877,10 @@
         <v>11304</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="F152" s="1">
         <v>8</v>
@@ -5813,7 +5889,7 @@
         <v>4403</v>
       </c>
       <c r="H152" s="1">
-        <v>4902</v>
+        <v>5000</v>
       </c>
       <c r="I152" s="1">
         <v>41</v>
@@ -5833,10 +5909,10 @@
         <v>11305</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E153" s="7" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="F153" s="1">
         <v>6</v>
@@ -5845,7 +5921,7 @@
         <v>4903</v>
       </c>
       <c r="H153" s="1">
-        <v>5402</v>
+        <v>5500</v>
       </c>
       <c r="I153" s="1">
         <v>47</v>
@@ -5865,10 +5941,10 @@
         <v>11306</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="E154" s="7" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="F154" s="1">
         <v>4</v>
@@ -5877,7 +5953,7 @@
         <v>5403</v>
       </c>
       <c r="H154" s="1">
-        <v>6402</v>
+        <v>6400</v>
       </c>
       <c r="I154" s="1">
         <v>51</v>
@@ -5897,10 +5973,10 @@
         <v>11307</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E155" s="7" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="F155" s="1">
         <v>3</v>
@@ -5909,7 +5985,7 @@
         <v>6403</v>
       </c>
       <c r="H155" s="1">
-        <v>7402</v>
+        <v>7500</v>
       </c>
       <c r="I155" s="1">
         <v>61</v>
@@ -5929,10 +6005,10 @@
         <v>11308</v>
       </c>
       <c r="D156" s="9" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E156" s="7" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="F156" s="1">
         <v>1</v>
@@ -5941,10 +6017,10 @@
         <v>7403</v>
       </c>
       <c r="H156" s="1">
-        <v>9402</v>
+        <v>8500</v>
       </c>
       <c r="I156" s="1">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="J156" s="1">
         <v>1</v>
@@ -5953,13 +6029,40 @@
         <v>1</v>
       </c>
       <c r="L156" s="1" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="157" customHeight="1" spans="3:12">
-      <c r="D157" s="5"/>
-      <c r="E157" s="7"/>
-      <c r="K157" s="2"/>
+      <c r="C157" s="1">
+        <v>11309</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F157" s="1">
+        <v>1</v>
+      </c>
+      <c r="G157" s="1">
+        <v>9003</v>
+      </c>
+      <c r="H157" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I157" s="1">
+        <v>91</v>
+      </c>
+      <c r="J157" s="1">
+        <v>1</v>
+      </c>
+      <c r="K157" s="2">
+        <v>1</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>160</v>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -842,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4973,7 +4973,7 @@
         <v>2000</v>
       </c>
       <c r="H121" s="1">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="I121" s="1">
         <v>100</v>
@@ -5735,7 +5735,7 @@
         <v>172</v>
       </c>
       <c r="F146" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G146" s="1">
         <v>6401</v>
@@ -6011,7 +6011,7 @@
         <v>190</v>
       </c>
       <c r="F156" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G156" s="1">
         <v>7403</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -842,12 +842,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -2392,7 +2392,7 @@
         <v>57</v>
       </c>
       <c r="F26" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G26" s="2">
         <v>4001</v>
@@ -2421,19 +2421,19 @@
         <v>59</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G27" s="2">
         <v>5001</v>
       </c>
       <c r="H27" s="2">
-        <v>6000</v>
+        <v>7000</v>
       </c>
       <c r="I27" s="2">
         <v>9</v>
       </c>
       <c r="J27" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K27" s="2">
         <v>1</v>
@@ -2450,19 +2450,19 @@
         <v>61</v>
       </c>
       <c r="F28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G28" s="2">
         <v>6703</v>
       </c>
       <c r="H28" s="2">
-        <v>6800</v>
+        <v>7800</v>
       </c>
       <c r="I28" s="2">
         <v>11</v>
       </c>
       <c r="J28" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K28" s="2">
         <v>1</v>
@@ -2479,13 +2479,13 @@
         <v>63</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G29" s="2">
         <v>4803</v>
       </c>
       <c r="H29" s="2">
-        <v>5800</v>
+        <v>6800</v>
       </c>
       <c r="I29" s="2">
         <v>7</v>
@@ -2595,13 +2595,13 @@
         <v>68</v>
       </c>
       <c r="F33" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G33" s="2">
         <v>7407</v>
       </c>
       <c r="H33" s="2">
-        <v>8500</v>
+        <v>9500</v>
       </c>
       <c r="I33" s="2">
         <v>13</v>
@@ -4214,7 +4214,7 @@
         <v>4</v>
       </c>
       <c r="J95" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="K95" s="2">
         <v>1</v>
@@ -5613,13 +5613,13 @@
         <v>165</v>
       </c>
       <c r="F142" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G142" s="1">
         <v>3001</v>
       </c>
       <c r="H142" s="1">
-        <v>3800</v>
+        <v>5500</v>
       </c>
       <c r="I142" s="1">
         <v>62</v>
@@ -5651,7 +5651,7 @@
         <v>5001</v>
       </c>
       <c r="H143" s="2">
-        <v>6000</v>
+        <v>8000</v>
       </c>
       <c r="I143" s="2">
         <v>61</v>
@@ -5677,13 +5677,13 @@
         <v>170</v>
       </c>
       <c r="F144" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G144" s="1">
         <v>5501</v>
       </c>
       <c r="H144" s="1">
-        <v>7500</v>
+        <v>8500</v>
       </c>
       <c r="I144" s="1">
         <v>47</v>
@@ -5709,10 +5709,10 @@
         <v>2</v>
       </c>
       <c r="G145" s="1">
-        <v>5501</v>
+        <v>6001</v>
       </c>
       <c r="H145" s="1">
-        <v>6500</v>
+        <v>8000</v>
       </c>
       <c r="I145" s="1">
         <v>67</v>
@@ -5735,13 +5735,13 @@
         <v>172</v>
       </c>
       <c r="F146" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G146" s="1">
         <v>6401</v>
       </c>
       <c r="H146" s="1">
-        <v>8400</v>
+        <v>10000</v>
       </c>
       <c r="I146" s="1">
         <v>91</v>
@@ -5799,7 +5799,7 @@
         <v>8501</v>
       </c>
       <c r="H148" s="1">
-        <v>9500</v>
+        <v>10500</v>
       </c>
       <c r="I148" s="1">
         <v>59</v>
@@ -5828,7 +5828,7 @@
         <v>9001</v>
       </c>
       <c r="H149" s="1">
-        <v>10000</v>
+        <v>11000</v>
       </c>
       <c r="I149" s="1">
         <v>61</v>
@@ -5953,7 +5953,7 @@
         <v>5403</v>
       </c>
       <c r="H154" s="1">
-        <v>6400</v>
+        <v>8000</v>
       </c>
       <c r="I154" s="1">
         <v>51</v>
@@ -5985,7 +5985,7 @@
         <v>6403</v>
       </c>
       <c r="H155" s="1">
-        <v>7500</v>
+        <v>9000</v>
       </c>
       <c r="I155" s="1">
         <v>61</v>
@@ -6011,13 +6011,13 @@
         <v>190</v>
       </c>
       <c r="F156" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G156" s="1">
         <v>7403</v>
       </c>
       <c r="H156" s="1">
-        <v>8500</v>
+        <v>10500</v>
       </c>
       <c r="I156" s="1">
         <v>71</v>
@@ -6049,7 +6049,7 @@
         <v>9003</v>
       </c>
       <c r="H157" s="1">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="I157" s="1">
         <v>91</v>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="198">
   <si>
     <t>#</t>
   </si>
@@ -486,6 +486,21 @@
   </si>
   <si>
     <t>道戒之源</t>
+  </si>
+  <si>
+    <t>神宠契约</t>
+  </si>
+  <si>
+    <t>仙宠契约</t>
+  </si>
+  <si>
+    <t>坐骑契约</t>
+  </si>
+  <si>
+    <t>英灵契约</t>
+  </si>
+  <si>
+    <t>深渊契约</t>
   </si>
   <si>
     <t>220016</t>
@@ -1641,7 +1656,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M157"/>
+  <dimension ref="A1:M163"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="1"/>
@@ -5218,7 +5233,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="129" customHeight="1" spans="3:12">
+    <row r="129" customHeight="1" spans="1:12">
       <c r="C129" s="1">
         <v>10043</v>
       </c>
@@ -5250,7 +5265,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="130" customHeight="1" spans="3:12">
+    <row r="130" customHeight="1" spans="1:12">
       <c r="C130" s="1">
         <v>10044</v>
       </c>
@@ -5282,347 +5297,327 @@
         <v>125</v>
       </c>
     </row>
-    <row r="132" customHeight="1" spans="3:12">
+    <row r="131" customHeight="1" spans="1:12">
+      <c r="C131" s="1">
+        <v>10045</v>
+      </c>
+      <c r="D131" s="6">
+        <v>180046</v>
+      </c>
+      <c r="E131" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F131" s="1">
+        <v>2</v>
+      </c>
+      <c r="G131" s="1">
+        <v>6000</v>
+      </c>
+      <c r="H131" s="1">
+        <v>7000</v>
+      </c>
+      <c r="I131" s="1">
+        <v>100</v>
+      </c>
+      <c r="J131" s="1">
+        <v>1</v>
+      </c>
+      <c r="K131" s="2">
+        <v>1</v>
+      </c>
+      <c r="L131" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="132" customHeight="1" spans="1:12">
       <c r="C132" s="1">
-        <v>11001</v>
-      </c>
-      <c r="D132" s="9" t="s">
-        <v>140</v>
+        <v>10046</v>
+      </c>
+      <c r="D132" s="6">
+        <v>180047</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>141</v>
       </c>
       <c r="F132" s="1">
+        <v>2</v>
+      </c>
+      <c r="G132" s="1">
+        <v>7000</v>
+      </c>
+      <c r="H132" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I132" s="1">
+        <v>100</v>
+      </c>
+      <c r="J132" s="1">
+        <v>1</v>
+      </c>
+      <c r="K132" s="2">
+        <v>1</v>
+      </c>
+      <c r="L132" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="133" customHeight="1" spans="1:12">
+      <c r="C133" s="1">
+        <v>10047</v>
+      </c>
+      <c r="D133" s="6">
+        <v>180048</v>
+      </c>
+      <c r="E133" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="F133" s="1">
+        <v>2</v>
+      </c>
+      <c r="G133" s="1">
+        <v>8000</v>
+      </c>
+      <c r="H133" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I133" s="1">
+        <v>100</v>
+      </c>
+      <c r="J133" s="1">
+        <v>1</v>
+      </c>
+      <c r="K133" s="2">
+        <v>1</v>
+      </c>
+      <c r="L133" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="134" customHeight="1" spans="1:12">
+      <c r="A134" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C134" s="1">
+        <v>10048</v>
+      </c>
+      <c r="D134" s="6">
+        <v>180049</v>
+      </c>
+      <c r="E134" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="F134" s="1">
+        <v>2</v>
+      </c>
+      <c r="G134" s="1">
+        <v>9000</v>
+      </c>
+      <c r="H134" s="1">
+        <v>10000</v>
+      </c>
+      <c r="I134" s="1">
+        <v>100</v>
+      </c>
+      <c r="J134" s="1">
+        <v>1</v>
+      </c>
+      <c r="K134" s="2">
+        <v>1</v>
+      </c>
+      <c r="L134" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="135" customHeight="1" spans="1:12">
+      <c r="A135" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C135" s="1">
+        <v>10049</v>
+      </c>
+      <c r="D135" s="6">
+        <v>180050</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="F135" s="1">
+        <v>2</v>
+      </c>
+      <c r="G135" s="1">
+        <v>10000</v>
+      </c>
+      <c r="H135" s="1">
+        <v>11000</v>
+      </c>
+      <c r="I135" s="1">
+        <v>100</v>
+      </c>
+      <c r="J135" s="1">
+        <v>1</v>
+      </c>
+      <c r="K135" s="2">
+        <v>1</v>
+      </c>
+      <c r="L135" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="138" customHeight="1" spans="1:12">
+      <c r="C138" s="1">
+        <v>11001</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>145</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="F138" s="1">
         <v>5</v>
       </c>
-      <c r="G132" s="1">
+      <c r="G138" s="1">
         <v>150</v>
       </c>
-      <c r="H132" s="1">
+      <c r="H138" s="1">
         <v>1200</v>
-      </c>
-      <c r="I132" s="1">
-        <v>20</v>
-      </c>
-      <c r="J132" s="1">
-        <v>2</v>
-      </c>
-      <c r="K132" s="2">
-        <v>1</v>
-      </c>
-      <c r="L132" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="133" customHeight="1" spans="3:12">
-      <c r="C133" s="1">
-        <v>11002</v>
-      </c>
-      <c r="D133" s="9" t="s">
-        <v>142</v>
-      </c>
-      <c r="E133" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F133" s="1">
-        <v>5</v>
-      </c>
-      <c r="G133" s="1">
-        <v>200</v>
-      </c>
-      <c r="H133" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I133" s="1">
-        <v>30</v>
-      </c>
-      <c r="J133" s="1">
-        <v>2</v>
-      </c>
-      <c r="K133" s="2">
-        <v>1</v>
-      </c>
-      <c r="L133" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="134" customHeight="1" spans="3:12">
-      <c r="C134" s="1">
-        <v>11003</v>
-      </c>
-      <c r="D134" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E134" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F134" s="1">
-        <v>15</v>
-      </c>
-      <c r="G134" s="1">
-        <v>1050</v>
-      </c>
-      <c r="H134" s="1">
-        <v>1500</v>
-      </c>
-      <c r="I134" s="1">
-        <v>51</v>
-      </c>
-      <c r="J134" s="1">
-        <v>2</v>
-      </c>
-      <c r="K134" s="2">
-        <v>1</v>
-      </c>
-      <c r="L134" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="135" customHeight="1" spans="3:12">
-      <c r="C135" s="1">
-        <v>11004</v>
-      </c>
-      <c r="D135" s="9" t="s">
-        <v>144</v>
-      </c>
-      <c r="E135" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="F135" s="1">
-        <v>5</v>
-      </c>
-      <c r="G135" s="1">
-        <v>4001</v>
-      </c>
-      <c r="H135" s="1">
-        <v>6000</v>
-      </c>
-      <c r="I135" s="1">
-        <v>79</v>
-      </c>
-      <c r="J135" s="1">
-        <v>2</v>
-      </c>
-      <c r="K135" s="2">
-        <v>1</v>
-      </c>
-      <c r="L135" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="136" customHeight="1" spans="3:12">
-      <c r="C136" s="1">
-        <v>11005</v>
-      </c>
-      <c r="D136" s="9" t="s">
-        <v>146</v>
-      </c>
-      <c r="E136" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="F136" s="1">
-        <v>20</v>
-      </c>
-      <c r="G136" s="1">
-        <v>101</v>
-      </c>
-      <c r="H136" s="1">
-        <v>500</v>
-      </c>
-      <c r="I136" s="1">
-        <v>10</v>
-      </c>
-      <c r="J136" s="1">
-        <v>1</v>
-      </c>
-      <c r="K136" s="2">
-        <v>1</v>
-      </c>
-      <c r="L136" s="1" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="137" customHeight="1" spans="3:12">
-      <c r="C137" s="1">
-        <v>11006</v>
-      </c>
-      <c r="D137" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="E137" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F137" s="1">
-        <v>15</v>
-      </c>
-      <c r="G137" s="1">
-        <v>501</v>
-      </c>
-      <c r="H137" s="1">
-        <v>1000</v>
-      </c>
-      <c r="I137" s="1">
-        <v>10</v>
-      </c>
-      <c r="J137" s="1">
-        <v>1</v>
-      </c>
-      <c r="K137" s="2">
-        <v>1</v>
-      </c>
-      <c r="L137" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="138" customHeight="1" spans="3:12">
-      <c r="C138" s="1">
-        <v>11007</v>
-      </c>
-      <c r="D138" s="9" t="s">
-        <v>152</v>
-      </c>
-      <c r="E138" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="F138" s="1">
-        <v>10</v>
-      </c>
-      <c r="G138" s="1">
-        <v>1001</v>
-      </c>
-      <c r="H138" s="1">
-        <v>1500</v>
       </c>
       <c r="I138" s="1">
         <v>20</v>
       </c>
       <c r="J138" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K138" s="2">
         <v>1</v>
       </c>
       <c r="L138" s="1" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="139" customHeight="1" spans="3:12">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="139" customHeight="1" spans="1:12">
       <c r="C139" s="1">
-        <v>11008</v>
+        <v>11002</v>
       </c>
       <c r="D139" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="E139" s="7" t="s">
-        <v>156</v>
+        <v>147</v>
+      </c>
+      <c r="E139" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="F139" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G139" s="1">
-        <v>1501</v>
+        <v>200</v>
       </c>
       <c r="H139" s="1">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="I139" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J139" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K139" s="2">
         <v>1</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="140" customHeight="1" spans="3:12">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="140" customHeight="1" spans="1:12">
       <c r="C140" s="1">
-        <v>11009</v>
+        <v>11003</v>
       </c>
       <c r="D140" s="9" t="s">
-        <v>158</v>
-      </c>
-      <c r="E140" s="7" t="s">
-        <v>159</v>
+        <v>149</v>
+      </c>
+      <c r="E140" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F140" s="1">
         <v>15</v>
       </c>
       <c r="G140" s="1">
-        <v>2001</v>
+        <v>1050</v>
       </c>
       <c r="H140" s="1">
-        <v>2500</v>
+        <v>1500</v>
       </c>
       <c r="I140" s="1">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J140" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K140" s="2">
         <v>1</v>
       </c>
       <c r="L140" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="141" customHeight="1" spans="3:12">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="141" customHeight="1" spans="1:12">
       <c r="C141" s="1">
-        <v>11010</v>
+        <v>11004</v>
       </c>
       <c r="D141" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="E141" s="7" t="s">
-        <v>162</v>
+        <v>149</v>
+      </c>
+      <c r="E141" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="F141" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G141" s="1">
-        <v>2501</v>
+        <v>4001</v>
       </c>
       <c r="H141" s="1">
-        <v>3000</v>
+        <v>6000</v>
       </c>
       <c r="I141" s="1">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="J141" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K141" s="2">
         <v>1</v>
       </c>
       <c r="L141" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="142" customHeight="1" spans="3:12">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="142" customHeight="1" spans="1:12">
       <c r="C142" s="1">
-        <v>11011</v>
+        <v>11005</v>
       </c>
       <c r="D142" s="9" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="E142" s="7" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="F142" s="1">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="G142" s="1">
-        <v>3001</v>
+        <v>101</v>
       </c>
       <c r="H142" s="1">
-        <v>5500</v>
+        <v>500</v>
       </c>
       <c r="I142" s="1">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="J142" s="1">
         <v>1</v>
@@ -5631,361 +5626,396 @@
         <v>1</v>
       </c>
       <c r="L142" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="143" customHeight="1" spans="3:12">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="143" customHeight="1" spans="1:12">
       <c r="C143" s="1">
-        <v>11012</v>
+        <v>11006</v>
       </c>
       <c r="D143" s="9" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="E143" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F143" s="2">
-        <v>2</v>
-      </c>
-      <c r="G143" s="2">
-        <v>5001</v>
-      </c>
-      <c r="H143" s="2">
-        <v>8000</v>
-      </c>
-      <c r="I143" s="2">
-        <v>61</v>
-      </c>
-      <c r="J143" s="2">
+        <v>155</v>
+      </c>
+      <c r="F143" s="1">
+        <v>15</v>
+      </c>
+      <c r="G143" s="1">
+        <v>501</v>
+      </c>
+      <c r="H143" s="1">
+        <v>1000</v>
+      </c>
+      <c r="I143" s="1">
+        <v>10</v>
+      </c>
+      <c r="J143" s="1">
         <v>1</v>
       </c>
       <c r="K143" s="2">
         <v>1</v>
       </c>
       <c r="L143" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="144" customHeight="1" spans="3:12">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="144" customHeight="1" spans="1:12">
       <c r="C144" s="1">
-        <v>11013</v>
+        <v>11007</v>
       </c>
       <c r="D144" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="E144" s="1" t="s">
-        <v>170</v>
+        <v>157</v>
+      </c>
+      <c r="E144" s="7" t="s">
+        <v>158</v>
       </c>
       <c r="F144" s="1">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="G144" s="1">
-        <v>5501</v>
+        <v>1001</v>
       </c>
       <c r="H144" s="1">
-        <v>8500</v>
+        <v>1500</v>
       </c>
       <c r="I144" s="1">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="J144" s="1">
         <v>1</v>
       </c>
       <c r="K144" s="2">
         <v>1</v>
+      </c>
+      <c r="L144" s="1" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="145" customHeight="1" spans="3:12">
       <c r="C145" s="1">
-        <v>11014</v>
+        <v>11008</v>
       </c>
       <c r="D145" s="9" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E145" s="7" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="F145" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G145" s="1">
-        <v>6001</v>
+        <v>1501</v>
       </c>
       <c r="H145" s="1">
-        <v>8000</v>
+        <v>2000</v>
       </c>
       <c r="I145" s="1">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="J145" s="1">
         <v>1</v>
       </c>
       <c r="K145" s="2">
         <v>1</v>
+      </c>
+      <c r="L145" s="1" t="s">
+        <v>162</v>
       </c>
     </row>
     <row r="146" customHeight="1" spans="3:12">
       <c r="C146" s="1">
-        <v>11015</v>
+        <v>11009</v>
       </c>
       <c r="D146" s="9" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="E146" s="7" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="F146" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="G146" s="1">
-        <v>6401</v>
+        <v>2001</v>
       </c>
       <c r="H146" s="1">
-        <v>10000</v>
+        <v>2500</v>
       </c>
       <c r="I146" s="1">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="J146" s="1">
         <v>1</v>
       </c>
       <c r="K146" s="2">
         <v>1</v>
+      </c>
+      <c r="L146" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="147" customHeight="1" spans="3:12">
       <c r="C147" s="1">
-        <v>11016</v>
+        <v>11010</v>
       </c>
       <c r="D147" s="9" t="s">
-        <v>173</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>174</v>
+        <v>166</v>
+      </c>
+      <c r="E147" s="7" t="s">
+        <v>167</v>
       </c>
       <c r="F147" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G147" s="1">
-        <v>8001</v>
+        <v>2501</v>
       </c>
       <c r="H147" s="1">
-        <v>10000</v>
+        <v>3000</v>
       </c>
       <c r="I147" s="1">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J147" s="1">
         <v>1</v>
       </c>
       <c r="K147" s="2">
         <v>1</v>
+      </c>
+      <c r="L147" s="1" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="148" customHeight="1" spans="3:12">
       <c r="C148" s="1">
-        <v>11017</v>
+        <v>11011</v>
       </c>
       <c r="D148" s="9" t="s">
-        <v>175</v>
-      </c>
-      <c r="E148" s="1" t="s">
-        <v>176</v>
+        <v>169</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>170</v>
       </c>
       <c r="F148" s="1">
         <v>2</v>
       </c>
       <c r="G148" s="1">
-        <v>8501</v>
+        <v>3001</v>
       </c>
       <c r="H148" s="1">
-        <v>10500</v>
+        <v>5500</v>
       </c>
       <c r="I148" s="1">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="J148" s="1">
         <v>1</v>
       </c>
       <c r="K148" s="2">
         <v>1</v>
+      </c>
+      <c r="L148" s="1" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="149" customHeight="1" spans="3:12">
       <c r="C149" s="1">
-        <v>11018</v>
+        <v>11012</v>
       </c>
       <c r="D149" s="9" t="s">
-        <v>177</v>
-      </c>
-      <c r="E149" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="F149" s="1">
+        <v>172</v>
+      </c>
+      <c r="E149" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F149" s="2">
         <v>2</v>
       </c>
-      <c r="G149" s="1">
-        <v>9001</v>
-      </c>
-      <c r="H149" s="1">
-        <v>11000</v>
-      </c>
-      <c r="I149" s="1">
+      <c r="G149" s="2">
+        <v>5001</v>
+      </c>
+      <c r="H149" s="2">
+        <v>8000</v>
+      </c>
+      <c r="I149" s="2">
         <v>61</v>
       </c>
-      <c r="J149" s="1">
+      <c r="J149" s="2">
         <v>1</v>
       </c>
       <c r="K149" s="2">
+        <v>1</v>
+      </c>
+      <c r="L149" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="150" customHeight="1" spans="3:12">
+      <c r="C150" s="1">
+        <v>11013</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="E150" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F150" s="1">
+        <v>2</v>
+      </c>
+      <c r="G150" s="1">
+        <v>5501</v>
+      </c>
+      <c r="H150" s="1">
+        <v>8500</v>
+      </c>
+      <c r="I150" s="1">
+        <v>47</v>
+      </c>
+      <c r="J150" s="1">
+        <v>1</v>
+      </c>
+      <c r="K150" s="2">
         <v>1</v>
       </c>
     </row>
     <row r="151" customHeight="1" spans="3:12">
       <c r="C151" s="1">
-        <v>11303</v>
+        <v>11014</v>
       </c>
       <c r="D151" s="9" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="E151" s="7" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F151" s="1">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="G151" s="1">
-        <v>3903</v>
+        <v>6001</v>
       </c>
       <c r="H151" s="1">
-        <v>4500</v>
+        <v>8000</v>
       </c>
       <c r="I151" s="1">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="J151" s="1">
         <v>1</v>
       </c>
       <c r="K151" s="2">
         <v>1</v>
-      </c>
-      <c r="L151" s="1" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="152" customHeight="1" spans="3:12">
       <c r="C152" s="1">
-        <v>11304</v>
+        <v>11015</v>
       </c>
       <c r="D152" s="9" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E152" s="7" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F152" s="1">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G152" s="1">
-        <v>4403</v>
+        <v>6401</v>
       </c>
       <c r="H152" s="1">
-        <v>5000</v>
+        <v>10000</v>
       </c>
       <c r="I152" s="1">
-        <v>41</v>
+        <v>91</v>
       </c>
       <c r="J152" s="1">
         <v>1</v>
       </c>
       <c r="K152" s="2">
         <v>1</v>
-      </c>
-      <c r="L152" s="1" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="153" customHeight="1" spans="3:12">
       <c r="C153" s="1">
-        <v>11305</v>
+        <v>11016</v>
       </c>
       <c r="D153" s="9" t="s">
-        <v>183</v>
-      </c>
-      <c r="E153" s="7" t="s">
-        <v>184</v>
+        <v>178</v>
+      </c>
+      <c r="E153" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="F153" s="1">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="G153" s="1">
-        <v>4903</v>
+        <v>8001</v>
       </c>
       <c r="H153" s="1">
-        <v>5500</v>
+        <v>10000</v>
       </c>
       <c r="I153" s="1">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="J153" s="1">
         <v>1</v>
       </c>
       <c r="K153" s="2">
         <v>1</v>
-      </c>
-      <c r="L153" s="1" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="154" customHeight="1" spans="3:12">
       <c r="C154" s="1">
-        <v>11306</v>
+        <v>11017</v>
       </c>
       <c r="D154" s="9" t="s">
-        <v>185</v>
-      </c>
-      <c r="E154" s="7" t="s">
-        <v>186</v>
+        <v>180</v>
+      </c>
+      <c r="E154" s="1" t="s">
+        <v>181</v>
       </c>
       <c r="F154" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G154" s="1">
-        <v>5403</v>
+        <v>8501</v>
       </c>
       <c r="H154" s="1">
-        <v>8000</v>
+        <v>10500</v>
       </c>
       <c r="I154" s="1">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="J154" s="1">
         <v>1</v>
       </c>
       <c r="K154" s="2">
         <v>1</v>
-      </c>
-      <c r="L154" s="1" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="155" customHeight="1" spans="3:12">
       <c r="C155" s="1">
-        <v>11307</v>
+        <v>11018</v>
       </c>
       <c r="D155" s="9" t="s">
-        <v>187</v>
-      </c>
-      <c r="E155" s="7" t="s">
-        <v>188</v>
+        <v>182</v>
+      </c>
+      <c r="E155" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="F155" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G155" s="1">
-        <v>6403</v>
+        <v>9001</v>
       </c>
       <c r="H155" s="1">
-        <v>9000</v>
+        <v>11000</v>
       </c>
       <c r="I155" s="1">
         <v>61</v>
@@ -5996,72 +6026,229 @@
       <c r="K155" s="2">
         <v>1</v>
       </c>
-      <c r="L155" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="156" customHeight="1" spans="3:12">
-      <c r="C156" s="1">
-        <v>11308</v>
-      </c>
-      <c r="D156" s="9" t="s">
-        <v>189</v>
-      </c>
-      <c r="E156" s="7" t="s">
-        <v>190</v>
-      </c>
-      <c r="F156" s="1">
-        <v>1</v>
-      </c>
-      <c r="G156" s="1">
-        <v>7403</v>
-      </c>
-      <c r="H156" s="1">
-        <v>10500</v>
-      </c>
-      <c r="I156" s="1">
-        <v>71</v>
-      </c>
-      <c r="J156" s="1">
-        <v>1</v>
-      </c>
-      <c r="K156" s="2">
-        <v>1</v>
-      </c>
-      <c r="L156" s="1" t="s">
-        <v>160</v>
-      </c>
     </row>
     <row r="157" customHeight="1" spans="3:12">
       <c r="C157" s="1">
+        <v>11303</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>184</v>
+      </c>
+      <c r="E157" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="F157" s="1">
+        <v>10</v>
+      </c>
+      <c r="G157" s="1">
+        <v>3903</v>
+      </c>
+      <c r="H157" s="1">
+        <v>4500</v>
+      </c>
+      <c r="I157" s="1">
+        <v>37</v>
+      </c>
+      <c r="J157" s="1">
+        <v>1</v>
+      </c>
+      <c r="K157" s="2">
+        <v>1</v>
+      </c>
+      <c r="L157" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="158" customHeight="1" spans="3:12">
+      <c r="C158" s="1">
+        <v>11304</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="E158" s="7" t="s">
+        <v>187</v>
+      </c>
+      <c r="F158" s="1">
+        <v>8</v>
+      </c>
+      <c r="G158" s="1">
+        <v>4403</v>
+      </c>
+      <c r="H158" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I158" s="1">
+        <v>41</v>
+      </c>
+      <c r="J158" s="1">
+        <v>1</v>
+      </c>
+      <c r="K158" s="2">
+        <v>1</v>
+      </c>
+      <c r="L158" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="159" customHeight="1" spans="3:12">
+      <c r="C159" s="1">
+        <v>11305</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>188</v>
+      </c>
+      <c r="E159" s="7" t="s">
+        <v>189</v>
+      </c>
+      <c r="F159" s="1">
+        <v>6</v>
+      </c>
+      <c r="G159" s="1">
+        <v>4903</v>
+      </c>
+      <c r="H159" s="1">
+        <v>5500</v>
+      </c>
+      <c r="I159" s="1">
+        <v>47</v>
+      </c>
+      <c r="J159" s="1">
+        <v>1</v>
+      </c>
+      <c r="K159" s="2">
+        <v>1</v>
+      </c>
+      <c r="L159" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" customHeight="1" spans="3:12">
+      <c r="C160" s="1">
+        <v>11306</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>190</v>
+      </c>
+      <c r="E160" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="F160" s="1">
+        <v>4</v>
+      </c>
+      <c r="G160" s="1">
+        <v>5403</v>
+      </c>
+      <c r="H160" s="1">
+        <v>8000</v>
+      </c>
+      <c r="I160" s="1">
+        <v>51</v>
+      </c>
+      <c r="J160" s="1">
+        <v>1</v>
+      </c>
+      <c r="K160" s="2">
+        <v>1</v>
+      </c>
+      <c r="L160" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="161" customHeight="1" spans="3:12">
+      <c r="C161" s="1">
+        <v>11307</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="E161" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="F161" s="1">
+        <v>3</v>
+      </c>
+      <c r="G161" s="1">
+        <v>6403</v>
+      </c>
+      <c r="H161" s="1">
+        <v>9000</v>
+      </c>
+      <c r="I161" s="1">
+        <v>61</v>
+      </c>
+      <c r="J161" s="1">
+        <v>1</v>
+      </c>
+      <c r="K161" s="2">
+        <v>1</v>
+      </c>
+      <c r="L161" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="162" customHeight="1" spans="3:12">
+      <c r="C162" s="1">
+        <v>11308</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>194</v>
+      </c>
+      <c r="E162" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="F162" s="1">
+        <v>1</v>
+      </c>
+      <c r="G162" s="1">
+        <v>7403</v>
+      </c>
+      <c r="H162" s="1">
+        <v>10500</v>
+      </c>
+      <c r="I162" s="1">
+        <v>71</v>
+      </c>
+      <c r="J162" s="1">
+        <v>1</v>
+      </c>
+      <c r="K162" s="2">
+        <v>1</v>
+      </c>
+      <c r="L162" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="163" customHeight="1" spans="3:12">
+      <c r="C163" s="1">
         <v>11309</v>
       </c>
-      <c r="D157" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="E157" s="7" t="s">
-        <v>192</v>
-      </c>
-      <c r="F157" s="1">
-        <v>1</v>
-      </c>
-      <c r="G157" s="1">
+      <c r="D163" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E163" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F163" s="1">
+        <v>1</v>
+      </c>
+      <c r="G163" s="1">
         <v>9003</v>
       </c>
-      <c r="H157" s="1">
+      <c r="H163" s="1">
         <v>12000</v>
       </c>
-      <c r="I157" s="1">
+      <c r="I163" s="1">
         <v>91</v>
       </c>
-      <c r="J157" s="1">
-        <v>1</v>
-      </c>
-      <c r="K157" s="2">
-        <v>1</v>
-      </c>
-      <c r="L157" s="1" t="s">
-        <v>160</v>
+      <c r="J163" s="1">
+        <v>1</v>
+      </c>
+      <c r="K163" s="2">
+        <v>1</v>
+      </c>
+      <c r="L163" s="1" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -66,7 +66,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="381" uniqueCount="198">
   <si>
     <t>#</t>
   </si>
@@ -5693,7 +5693,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="145" customHeight="1" spans="3:12">
+    <row r="145" customHeight="1" spans="1:12">
       <c r="C145" s="1">
         <v>11008</v>
       </c>
@@ -5725,7 +5725,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="146" customHeight="1" spans="3:12">
+    <row r="146" customHeight="1" spans="1:12">
       <c r="C146" s="1">
         <v>11009</v>
       </c>
@@ -5757,7 +5757,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="147" customHeight="1" spans="3:12">
+    <row r="147" customHeight="1" spans="1:12">
       <c r="C147" s="1">
         <v>11010</v>
       </c>
@@ -5789,7 +5789,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="148" customHeight="1" spans="3:12">
+    <row r="148" customHeight="1" spans="1:12">
       <c r="C148" s="1">
         <v>11011</v>
       </c>
@@ -5806,7 +5806,7 @@
         <v>3001</v>
       </c>
       <c r="H148" s="1">
-        <v>5500</v>
+        <v>7000</v>
       </c>
       <c r="I148" s="1">
         <v>62</v>
@@ -5821,7 +5821,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="149" customHeight="1" spans="3:12">
+    <row r="149" customHeight="1" spans="1:12">
       <c r="C149" s="1">
         <v>11012</v>
       </c>
@@ -5853,7 +5853,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="150" customHeight="1" spans="3:12">
+    <row r="150" customHeight="1" spans="1:12">
       <c r="C150" s="1">
         <v>11013</v>
       </c>
@@ -5882,7 +5882,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" customHeight="1" spans="3:12">
+    <row r="151" customHeight="1" spans="1:12">
+      <c r="A151" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="C151" s="1">
         <v>11014</v>
       </c>
@@ -5911,7 +5917,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" customHeight="1" spans="3:12">
+    <row r="152" customHeight="1" spans="1:12">
       <c r="C152" s="1">
         <v>11015</v>
       </c>
@@ -5940,7 +5946,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" customHeight="1" spans="3:12">
+    <row r="153" customHeight="1" spans="1:12">
       <c r="C153" s="1">
         <v>11016</v>
       </c>
@@ -5969,7 +5975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" customHeight="1" spans="3:12">
+    <row r="154" customHeight="1" spans="1:12">
       <c r="C154" s="1">
         <v>11017</v>
       </c>
@@ -5998,7 +6004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" customHeight="1" spans="3:12">
+    <row r="155" customHeight="1" spans="1:12">
       <c r="C155" s="1">
         <v>11018</v>
       </c>
@@ -6027,7 +6033,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" customHeight="1" spans="3:12">
+    <row r="157" customHeight="1" spans="1:12">
       <c r="C157" s="1">
         <v>11303</v>
       </c>
@@ -6059,7 +6065,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="158" customHeight="1" spans="3:12">
+    <row r="158" customHeight="1" spans="1:12">
       <c r="C158" s="1">
         <v>11304</v>
       </c>
@@ -6091,7 +6097,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="159" customHeight="1" spans="3:12">
+    <row r="159" customHeight="1" spans="1:12">
       <c r="C159" s="1">
         <v>11305</v>
       </c>
@@ -6123,7 +6129,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="160" customHeight="1" spans="3:12">
+    <row r="160" customHeight="1" spans="1:12">
       <c r="C160" s="1">
         <v>11306</v>
       </c>

--- a/Excel/InfiniteDropConfig.xlsx
+++ b/Excel/InfiniteDropConfig.xlsx
@@ -5308,7 +5308,7 @@
         <v>140</v>
       </c>
       <c r="F131" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G131" s="1">
         <v>6000</v>
@@ -5340,7 +5340,7 @@
         <v>141</v>
       </c>
       <c r="F132" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" s="1">
         <v>7000</v>
@@ -5372,7 +5372,7 @@
         <v>142</v>
       </c>
       <c r="F133" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G133" s="1">
         <v>8000</v>
